--- a/salidas/empresas/ANET.xlsx
+++ b/salidas/empresas/ANET.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,54 +447,54 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B2" t="n">
@@ -501,7 +513,7 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B3" t="n">
@@ -520,7 +532,7 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B4" t="n">
@@ -545,7 +557,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B5" t="n">
@@ -570,7 +582,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B6" t="n">
@@ -595,7 +607,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B7" t="n">
@@ -620,7 +632,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B8" t="n">
@@ -645,7 +657,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B9" t="n">
@@ -670,7 +682,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B10" t="n">
@@ -695,7 +707,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B11" t="n">
@@ -720,7 +732,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B12" t="n">
@@ -745,7 +757,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B13" t="n">
@@ -770,7 +782,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B14" t="n">
@@ -795,7 +807,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B15" t="n">
@@ -820,7 +832,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B16" t="n">
@@ -845,7 +857,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B17" t="n">
@@ -870,7 +882,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B18" t="n">
@@ -895,7 +907,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B19" t="n">
@@ -920,7 +932,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B20" t="n">
@@ -945,7 +957,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B21" t="n">
@@ -970,7 +982,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B22" t="n">
@@ -999,7 +1011,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B23" t="n">
@@ -1028,7 +1040,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B24" t="n">
@@ -1057,7 +1069,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B25" t="n">
@@ -1086,7 +1098,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B26" t="n">
@@ -1115,7 +1127,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B27" t="n">
@@ -1144,7 +1156,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B28" t="n">
@@ -1173,7 +1185,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B29" t="n">
@@ -1202,7 +1214,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B30" t="n">
@@ -1231,7 +1243,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B31" t="n">
@@ -1260,7 +1272,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B32" t="n">
@@ -1289,7 +1301,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B33" t="n">
@@ -1318,7 +1330,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B34" t="n">
@@ -1347,7 +1359,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B35" t="n">
@@ -1376,7 +1388,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B36" t="n">
@@ -1405,7 +1417,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B37" t="n">
@@ -1434,7 +1446,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B38" t="n">
@@ -1463,7 +1475,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B39" t="n">
@@ -1492,7 +1504,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B40" t="n">
@@ -1521,7 +1533,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B41" t="n">
@@ -1550,7 +1562,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B42" t="n">
@@ -1579,7 +1591,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B43" t="n">
@@ -1608,7 +1620,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B44" t="n">
@@ -1637,7 +1649,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B45" t="n">
@@ -1666,7 +1678,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B46" t="n">
@@ -1695,7 +1707,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B47" t="n">
@@ -1724,7 +1736,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B48" t="n">
@@ -1753,7 +1765,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B49" t="n">
@@ -1782,7 +1794,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B50" t="n">
@@ -1811,7 +1823,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B51" t="n">
@@ -1840,7 +1852,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B52" t="n">
@@ -1869,7 +1881,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B53" t="n">
@@ -1898,7 +1910,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B54" t="n">
@@ -1927,7 +1939,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B55" t="n">
@@ -1956,7 +1968,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B56" t="n">
@@ -1985,7 +1997,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B57" t="n">
@@ -2014,7 +2026,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B58" t="n">
@@ -2043,7 +2055,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B59" t="n">
@@ -2072,7 +2084,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B60" t="n">
@@ -2101,7 +2113,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B61" t="n">
@@ -2130,7 +2142,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B62" t="n">
@@ -2159,7 +2171,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B63" t="n">
@@ -2188,7 +2200,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B64" t="n">
@@ -2217,7 +2229,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B65" t="n">
@@ -2246,7 +2258,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B66" t="n">
@@ -2275,7 +2287,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B67" t="n">
@@ -2304,7 +2316,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B68" t="n">
@@ -2333,7 +2345,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B69" t="n">
@@ -2362,7 +2374,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B70" t="n">
@@ -2391,7 +2403,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B71" t="n">
@@ -2420,7 +2432,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B72" t="n">
@@ -2449,7 +2461,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B73" t="n">
@@ -2478,7 +2490,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B74" t="n">
@@ -2507,7 +2519,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B75" t="n">
@@ -2536,7 +2548,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B76" t="n">
@@ -2565,7 +2577,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B77" t="n">
@@ -2594,7 +2606,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B78" t="n">
@@ -2623,7 +2635,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B79" t="n">
@@ -2652,7 +2664,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B80" t="n">
@@ -2681,7 +2693,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B81" t="n">
@@ -2710,7 +2722,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B82" t="n">
@@ -2739,7 +2751,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B83" t="n">
@@ -2768,7 +2780,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B84" t="n">
@@ -2797,7 +2809,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B85" t="n">
@@ -2826,7 +2838,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B86" t="n">
@@ -2855,7 +2867,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B87" t="n">
@@ -2884,7 +2896,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B88" t="n">
@@ -2913,7 +2925,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B89" t="n">
@@ -2942,7 +2954,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B90" t="n">
@@ -2971,7 +2983,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B91" t="n">
@@ -3000,7 +3012,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B92" t="n">
@@ -3029,7 +3041,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B93" t="n">
@@ -3058,7 +3070,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B94" t="n">
@@ -3087,7 +3099,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B95" t="n">
@@ -3116,7 +3128,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B96" t="n">
@@ -3145,7 +3157,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B97" t="n">
@@ -3174,7 +3186,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B98" t="n">
@@ -3203,7 +3215,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B99" t="n">
@@ -3232,7 +3244,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B100" t="n">
@@ -3261,7 +3273,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B101" t="n">
@@ -3290,7 +3302,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B102" t="n">
@@ -3319,7 +3331,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B103" t="n">
@@ -3348,7 +3360,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B104" t="n">
@@ -3377,7 +3389,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B105" t="n">
@@ -3406,7 +3418,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B106" t="n">
@@ -3435,7 +3447,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B107" t="n">
@@ -3464,7 +3476,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B108" t="n">
@@ -3493,7 +3505,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B109" t="n">
@@ -3522,7 +3534,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B110" t="n">
@@ -3551,7 +3563,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B111" t="n">
@@ -3580,7 +3592,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B112" t="n">
@@ -3609,7 +3621,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B113" t="n">
@@ -3638,7 +3650,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B114" t="n">
@@ -3667,7 +3679,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B115" t="n">
@@ -3696,7 +3708,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B116" t="n">
@@ -3725,7 +3737,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B117" t="n">
@@ -3754,7 +3766,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B118" t="n">
@@ -3783,7 +3795,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B119" t="n">
@@ -3812,7 +3824,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B120" t="n">
@@ -3841,7 +3853,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B121" t="n">
@@ -3870,7 +3882,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B122" t="n">
@@ -3899,7 +3911,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B123" t="n">
@@ -3928,7 +3940,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B124" t="n">
@@ -3957,7 +3969,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B125" t="n">
@@ -3986,7 +3998,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B126" t="n">
@@ -4015,7 +4027,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B127" t="n">
@@ -4044,7 +4056,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B128" t="n">
@@ -4073,7 +4085,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B129" t="n">
@@ -4102,7 +4114,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B130" t="n">
@@ -4131,7 +4143,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B131" t="n">
@@ -4160,7 +4172,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B132" t="n">
@@ -4189,7 +4201,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B133" t="n">
@@ -4218,7 +4230,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B134" t="n">
@@ -4247,7 +4259,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B135" t="n">
@@ -4276,7 +4288,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B136" t="n">
@@ -4305,7 +4317,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B137" t="n">
@@ -4334,7 +4346,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B138" t="n">
@@ -4363,7 +4375,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B139" t="n">
@@ -4392,7 +4404,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B140" t="n">
@@ -4421,7 +4433,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B141" t="n">
@@ -4450,7 +4462,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B142" t="n">
@@ -4479,7 +4491,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B143" t="n">
@@ -4508,7 +4520,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B144" t="n">
@@ -4537,7 +4549,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B145" t="n">
@@ -4566,7 +4578,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B146" t="n">
@@ -4595,7 +4607,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B147" t="n">
@@ -4624,7 +4636,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B148" t="n">
@@ -4653,32 +4665,32 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B149" t="n">
-        <v>203.4700012207031</v>
+        <v>205.6999969482422</v>
       </c>
       <c r="C149" t="n">
-        <v>203.4700012207031</v>
+        <v>205.6999969482422</v>
       </c>
       <c r="D149" t="n">
-        <v>79384400</v>
+        <v>82941300</v>
       </c>
       <c r="E149" t="n">
         <v>3.16</v>
       </c>
       <c r="F149" t="n">
-        <v>64.38924089262757</v>
+        <v>65.09493574311462</v>
       </c>
       <c r="G149" t="n">
         <v>1261224648</v>
       </c>
       <c r="H149" t="n">
-        <v>256621380668.1409</v>
+        <v>259433906244.6478</v>
       </c>
       <c r="I149" t="n">
-        <v>0.06294231572930693</v>
+        <v>0.06576251116843064</v>
       </c>
     </row>
   </sheetData>
@@ -4710,75 +4722,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>41859</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -4814,13 +4826,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>41950</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -4856,13 +4868,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>42139</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -4898,13 +4910,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>41859</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -4940,13 +4952,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>41950</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -4982,13 +4994,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>42425</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -5015,7 +5027,7 @@
       <c r="I7" t="n">
         <v>0.079375</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>42425</v>
       </c>
       <c r="K7" t="n">
@@ -5028,13 +5040,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>42139</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -5061,7 +5073,7 @@
       <c r="I8" t="n">
         <v>0.08812500000000001</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>42425</v>
       </c>
       <c r="K8" t="n">
@@ -5074,13 +5086,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>42223</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -5107,7 +5119,7 @@
       <c r="I9" t="n">
         <v>0.08749999999999999</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>42425</v>
       </c>
       <c r="K9" t="n">
@@ -5120,13 +5132,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>42314</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -5153,7 +5165,7 @@
       <c r="I10" t="n">
         <v>0.093125</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>42425</v>
       </c>
       <c r="K10" t="n">
@@ -5166,13 +5178,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>42425</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -5199,7 +5211,7 @@
       <c r="I11" t="n">
         <v>0.10375</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>42425</v>
       </c>
       <c r="K11" t="n">
@@ -5212,13 +5224,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>42495</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -5245,7 +5257,7 @@
       <c r="I12" t="n">
         <v>0.1125</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>42495</v>
       </c>
       <c r="K12" t="n">
@@ -5258,13 +5270,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>42587</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -5291,7 +5303,7 @@
       <c r="I13" t="n">
         <v>0.125</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>42587</v>
       </c>
       <c r="K13" t="n">
@@ -5304,13 +5316,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -5337,7 +5349,7 @@
       <c r="I14" t="n">
         <v>0.14375</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="K14" t="n">
@@ -5350,13 +5362,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>42783</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -5383,7 +5395,7 @@
       <c r="I15" t="n">
         <v>0.155625</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>42783</v>
       </c>
       <c r="K15" t="n">
@@ -5396,13 +5408,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>42863</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -5429,7 +5441,7 @@
       <c r="I16" t="n">
         <v>0.1925</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>42863</v>
       </c>
       <c r="K16" t="n">
@@ -5442,13 +5454,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>42951</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -5475,7 +5487,7 @@
       <c r="I17" t="n">
         <v>0.240625</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>42951</v>
       </c>
       <c r="K17" t="n">
@@ -5488,13 +5500,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>43042</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -5521,7 +5533,7 @@
       <c r="I18" t="n">
         <v>0.3025</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>43042</v>
       </c>
       <c r="K18" t="n">
@@ -5534,13 +5546,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>43151</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -5567,7 +5579,7 @@
       <c r="I19" t="n">
         <v>0.33375</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>43151</v>
       </c>
       <c r="K19" t="n">
@@ -5580,13 +5592,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>43224</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -5613,7 +5625,7 @@
       <c r="I20" t="n">
         <v>0.37875</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>43224</v>
       </c>
       <c r="K20" t="n">
@@ -5626,13 +5638,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>43320</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -5659,7 +5671,7 @@
       <c r="I21" t="n">
         <v>0.1675</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>43320</v>
       </c>
       <c r="K21" t="n">
@@ -5672,13 +5684,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>43409</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -5705,7 +5717,7 @@
       <c r="I22" t="n">
         <v>0.1925</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>43409</v>
       </c>
       <c r="K22" t="n">
@@ -5718,13 +5730,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>43511</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -5751,7 +5763,7 @@
       <c r="I23" t="n">
         <v>0.243125</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>43511</v>
       </c>
       <c r="K23" t="n">
@@ -5764,13 +5776,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>43591</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -5797,7 +5809,7 @@
       <c r="I24" t="n">
         <v>0.285625</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>43591</v>
       </c>
       <c r="K24" t="n">
@@ -5810,13 +5822,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>43679</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -5843,7 +5855,7 @@
       <c r="I25" t="n">
         <v>0.56125</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>43679</v>
       </c>
       <c r="K25" t="n">
@@ -5856,13 +5868,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>43770</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -5889,7 +5901,7 @@
       <c r="I26" t="n">
         <v>0.593125</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>43770</v>
       </c>
       <c r="K26" t="n">
@@ -5902,13 +5914,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>43875</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -5935,7 +5947,7 @@
       <c r="I27" t="n">
         <v>0.665</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>43875</v>
       </c>
       <c r="K27" t="n">
@@ -5948,13 +5960,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>43957</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -5981,7 +5993,7 @@
       <c r="I28" t="n">
         <v>0.61875</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>43957</v>
       </c>
       <c r="K28" t="n">
@@ -5994,13 +6006,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>44048</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -6027,7 +6039,7 @@
       <c r="I29" t="n">
         <v>0.5875</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>44048</v>
       </c>
       <c r="K29" t="n">
@@ -6040,13 +6052,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>44138</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -6073,7 +6085,7 @@
       <c r="I30" t="n">
         <v>0.558125</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>44138</v>
       </c>
       <c r="K30" t="n">
@@ -6086,13 +6098,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>44246</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -6119,7 +6131,7 @@
       <c r="I31" t="n">
         <v>0.499375</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>44246</v>
       </c>
       <c r="K31" t="n">
@@ -6132,13 +6144,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -6165,7 +6177,7 @@
       <c r="I32" t="n">
         <v>0.533125</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="K32" t="n">
@@ -6178,13 +6190,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>44411</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -6211,7 +6223,7 @@
       <c r="I33" t="n">
         <v>0.573125</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>44411</v>
       </c>
       <c r="K33" t="n">
@@ -6224,13 +6236,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>44502</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -6257,7 +6269,7 @@
       <c r="I34" t="n">
         <v>0.6162500000000001</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>44502</v>
       </c>
       <c r="K34" t="n">
@@ -6270,13 +6282,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>44607</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -6303,7 +6315,7 @@
       <c r="I35" t="n">
         <v>0.6575</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>44607</v>
       </c>
       <c r="K35" t="n">
@@ -6316,13 +6328,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>44684</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -6349,7 +6361,7 @@
       <c r="I36" t="n">
         <v>0.7281249999999999</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>44684</v>
       </c>
       <c r="K36" t="n">
@@ -6362,13 +6374,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>44775</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -6395,7 +6407,7 @@
       <c r="I37" t="n">
         <v>0.8087499999999999</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>44775</v>
       </c>
       <c r="K37" t="n">
@@ -6408,13 +6420,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -6441,7 +6453,7 @@
       <c r="I38" t="n">
         <v>0.9156249999999999</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="K38" t="n">
@@ -6454,13 +6466,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>44971</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -6487,7 +6499,7 @@
       <c r="I39" t="n">
         <v>1.0675</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>44971</v>
       </c>
       <c r="K39" t="n">
@@ -6500,13 +6512,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>45048</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -6533,7 +6545,7 @@
       <c r="I40" t="n">
         <v>1.2</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>45048</v>
       </c>
       <c r="K40" t="n">
@@ -6546,13 +6558,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -6579,7 +6591,7 @@
       <c r="I41" t="n">
         <v>1.3525</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="K41" t="n">
@@ -6592,13 +6604,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -6625,7 +6637,7 @@
       <c r="I42" t="n">
         <v>1.5</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="K42" t="n">
@@ -6638,13 +6650,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>45335</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -6671,7 +6683,7 @@
       <c r="I43" t="n">
         <v>1.645</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>45335</v>
       </c>
       <c r="K43" t="n">
@@ -6684,13 +6696,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>45420</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -6717,7 +6729,7 @@
       <c r="I44" t="n">
         <v>1.7975</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>45420</v>
       </c>
       <c r="K44" t="n">
@@ -6730,13 +6742,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -6763,7 +6775,7 @@
       <c r="I45" t="n">
         <v>1.93</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="K45" t="n">
@@ -6776,13 +6788,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>45604</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -6809,7 +6821,7 @@
       <c r="I46" t="n">
         <v>2.0825</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>45604</v>
       </c>
       <c r="K46" t="n">
@@ -6822,13 +6834,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>45707</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -6855,7 +6867,7 @@
       <c r="I47" t="n">
         <v>2.23</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>45707</v>
       </c>
       <c r="K47" t="n">
@@ -6868,13 +6880,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>45784</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -6901,7 +6913,7 @@
       <c r="I48" t="n">
         <v>2.3725</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>45784</v>
       </c>
       <c r="K48" t="n">
@@ -6914,13 +6926,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -6947,7 +6959,7 @@
       <c r="I49" t="n">
         <v>2.5525</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="K49" t="n">
@@ -6960,13 +6972,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>45966</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -6993,7 +7005,7 @@
       <c r="I50" t="n">
         <v>2.64</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>45966</v>
       </c>
       <c r="K50" t="n">
@@ -7006,13 +7018,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>46070</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -7039,7 +7051,7 @@
       <c r="I51" t="n">
         <v>2.75</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>46070</v>
       </c>
       <c r="K51" t="n">
@@ -7052,13 +7064,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>46148</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -7085,7 +7097,7 @@
       <c r="I52" t="n">
         <v>2.91</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>46148</v>
       </c>
       <c r="K52" t="n">
@@ -7098,13 +7110,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>46239</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -7131,7 +7143,7 @@
       <c r="I53" t="n">
         <v>3.16</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>46239</v>
       </c>
       <c r="K53" t="n">
@@ -7168,52 +7180,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>41852</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>41859</v>
       </c>
       <c r="C2" t="n">
@@ -7242,10 +7254,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>41943</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>41950</v>
       </c>
       <c r="C3" t="n">
@@ -7274,10 +7286,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>42069</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>42075</v>
       </c>
       <c r="C4" t="n">
@@ -7306,10 +7318,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>42132</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>42139</v>
       </c>
       <c r="C5" t="n">
@@ -7338,10 +7350,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>42216</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>42223</v>
       </c>
       <c r="C6" t="n">
@@ -7370,10 +7382,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>42307</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>42314</v>
       </c>
       <c r="C7" t="n">
@@ -7402,10 +7414,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>42419</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>42425</v>
       </c>
       <c r="C8" t="n">
@@ -7434,10 +7446,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>42489</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>42495</v>
       </c>
       <c r="C9" t="n">
@@ -7466,10 +7478,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>42580</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>42587</v>
       </c>
       <c r="C10" t="n">
@@ -7498,10 +7510,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>42671</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="C11" t="n">
@@ -7530,10 +7542,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>42776</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>42783</v>
       </c>
       <c r="C12" t="n">
@@ -7562,10 +7574,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>42853</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>42863</v>
       </c>
       <c r="C13" t="n">
@@ -7594,10 +7606,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>42944</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>42951</v>
       </c>
       <c r="C14" t="n">
@@ -7626,10 +7638,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>43035</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>43042</v>
       </c>
       <c r="C15" t="n">
@@ -7658,10 +7670,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>43140</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>43151</v>
       </c>
       <c r="C16" t="n">
@@ -7690,10 +7702,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>43217</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>43224</v>
       </c>
       <c r="C17" t="n">
@@ -7722,10 +7734,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>43312</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>43320</v>
       </c>
       <c r="C18" t="n">
@@ -7754,10 +7766,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>43399</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>43409</v>
       </c>
       <c r="C19" t="n">
@@ -7786,10 +7798,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>43504</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>43511</v>
       </c>
       <c r="C20" t="n">
@@ -7818,10 +7830,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>43581</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>43591</v>
       </c>
       <c r="C21" t="n">
@@ -7850,10 +7862,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>43672</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>43679</v>
       </c>
       <c r="C22" t="n">
@@ -7882,10 +7894,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>43763</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>43770</v>
       </c>
       <c r="C23" t="n">
@@ -7914,10 +7926,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>43871</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>43875</v>
       </c>
       <c r="C24" t="n">
@@ -7946,10 +7958,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>43952</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>43957</v>
       </c>
       <c r="C25" t="n">
@@ -7978,10 +7990,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>44041</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>44048</v>
       </c>
       <c r="C26" t="n">
@@ -8010,10 +8022,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>44131</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>44138</v>
       </c>
       <c r="C27" t="n">
@@ -8042,10 +8054,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>44239</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>44246</v>
       </c>
       <c r="C28" t="n">
@@ -8074,10 +8086,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>44319</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="C29" t="n">
@@ -8106,10 +8118,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>44405</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>44411</v>
       </c>
       <c r="C30" t="n">
@@ -8138,10 +8150,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>44496</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>44502</v>
       </c>
       <c r="C31" t="n">
@@ -8170,10 +8182,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>44600</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>44607</v>
       </c>
       <c r="C32" t="n">
@@ -8202,10 +8214,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>44678</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>44684</v>
       </c>
       <c r="C33" t="n">
@@ -8234,10 +8246,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>44769</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>44775</v>
       </c>
       <c r="C34" t="n">
@@ -8266,10 +8278,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>44860</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="C35" t="n">
@@ -8298,10 +8310,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>44965</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>44971</v>
       </c>
       <c r="C36" t="n">
@@ -8330,10 +8342,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>45042</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>45048</v>
       </c>
       <c r="C37" t="n">
@@ -8362,10 +8374,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>45133</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="C38" t="n">
@@ -8394,10 +8406,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>45224</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="C39" t="n">
@@ -8426,10 +8438,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>45329</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>45335</v>
       </c>
       <c r="C40" t="n">
@@ -8458,10 +8470,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>45414</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>45420</v>
       </c>
       <c r="C41" t="n">
@@ -8490,10 +8502,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>45499</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="C42" t="n">
@@ -8522,10 +8534,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>45600</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>45604</v>
       </c>
       <c r="C43" t="n">
@@ -8554,10 +8566,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>45700</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>45707</v>
       </c>
       <c r="C44" t="n">
@@ -8586,10 +8598,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>45778</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>45784</v>
       </c>
       <c r="C45" t="n">
@@ -8618,10 +8630,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>45869</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="C46" t="n">
@@ -8650,10 +8662,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>45960</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>45966</v>
       </c>
       <c r="C47" t="n">
@@ -8682,10 +8694,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>46063</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>46070</v>
       </c>
       <c r="C48" t="n">
@@ -8714,10 +8726,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>46142</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>46148</v>
       </c>
       <c r="C49" t="n">
@@ -8746,10 +8758,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>46233</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>46239</v>
       </c>
       <c r="C50" t="n">
@@ -8796,12 +8808,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
